--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.50045686914788</v>
+        <v>7.71882424123653</v>
       </c>
       <c r="D2" t="n">
-        <v>44.51980490861294</v>
+        <v>7.234468297649603</v>
       </c>
       <c r="E2" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F2" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.55486854850531</v>
+        <v>10.49016613913211</v>
       </c>
       <c r="D3" t="n">
-        <v>47.28305837852272</v>
+        <v>7.683496986509943</v>
       </c>
       <c r="E3" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F3" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.72083336152665</v>
+        <v>9.217135421248081</v>
       </c>
       <c r="D4" t="n">
-        <v>29.89231163074999</v>
+        <v>4.857500639996873</v>
       </c>
       <c r="E4" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F4" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.8595133795823</v>
+        <v>9.889670924182123</v>
       </c>
       <c r="D5" t="n">
-        <v>30.05731111109826</v>
+        <v>4.884313055553467</v>
       </c>
       <c r="E5" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F5" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>49.16887095143422</v>
+        <v>7.989941529608061</v>
       </c>
       <c r="D6" t="n">
-        <v>18.91740966966491</v>
+        <v>3.074079071320547</v>
       </c>
       <c r="E6" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F6" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>76.67344616630075</v>
+        <v>12.45943500202387</v>
       </c>
       <c r="D7" t="n">
-        <v>45.93422687285266</v>
+        <v>7.464311866838558</v>
       </c>
       <c r="E7" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F7" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.57591979362873</v>
+        <v>5.131086966464668</v>
       </c>
       <c r="D8" t="n">
-        <v>12.70937728114264</v>
+        <v>2.065273808185679</v>
       </c>
       <c r="E8" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F8" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.68275247906009</v>
+        <v>5.148447277847264</v>
       </c>
       <c r="D9" t="n">
-        <v>28.3806031027995</v>
+        <v>4.611848004204919</v>
       </c>
       <c r="E9" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F9" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.6684663117032</v>
+        <v>3.35862577565177</v>
       </c>
       <c r="D10" t="n">
-        <v>21.37095504692601</v>
+        <v>3.472780195125477</v>
       </c>
       <c r="E10" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F10" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.79906426542384</v>
+        <v>5.329847943131374</v>
       </c>
       <c r="D11" t="n">
-        <v>32.02719840001463</v>
+        <v>5.204419740002378</v>
       </c>
       <c r="E11" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F11" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.51195396651087</v>
+        <v>4.958192519558017</v>
       </c>
       <c r="D12" t="n">
-        <v>30.28622249231287</v>
+        <v>4.921511155000842</v>
       </c>
       <c r="E12" t="n">
-        <v>16.79032776190131</v>
+        <v>2.728428261308963</v>
       </c>
       <c r="F12" t="n">
-        <v>10.68021574059601</v>
+        <v>1.735535057846851</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
